--- a/out/production/InventorySearch/components.xlsx
+++ b/out/production/InventorySearch/components.xlsx
@@ -1,24 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SchoeffmannF\Documents\java projects\InventorySearch\src\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C5ECA6-1CC4-40AF-8E0B-4BA028D8BA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37710" windowHeight="21840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="motherboards" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Processors" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="ram sticks" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Graphics Cards" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="storage" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Power Supplies" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="CPU Cooler" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Cases" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Fans" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="motherboards" sheetId="1" r:id="rId1"/>
+    <sheet name="Processors" sheetId="2" r:id="rId2"/>
+    <sheet name="ram sticks" sheetId="3" r:id="rId3"/>
+    <sheet name="Graphics Cards" sheetId="4" r:id="rId4"/>
+    <sheet name="storage" sheetId="5" r:id="rId5"/>
+    <sheet name="Power Supplies" sheetId="6" r:id="rId6"/>
+    <sheet name="CPU Cooler" sheetId="7" r:id="rId7"/>
+    <sheet name="Cases" sheetId="8" r:id="rId8"/>
+    <sheet name="Fans" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -30,781 +35,763 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="249">
   <si>
-    <t xml:space="preserve">Brand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Socket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAM Gen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAM Slots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Form Factor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.2 Slots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built-in-Wifi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max RAM Capacity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCIe Slots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SATA Slots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASRock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B760 PRO RS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LGA 1700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDR5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">256 GB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1x 5.0x16, 1x4.0x16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prime B760-PLUS D4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192 GB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">msi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H410 Pro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LGA 1200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64 GB</t>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Socket</t>
+  </si>
+  <si>
+    <t>RAM Gen.</t>
+  </si>
+  <si>
+    <t>RAM Slots</t>
+  </si>
+  <si>
+    <t>Form Factor</t>
+  </si>
+  <si>
+    <t>M.2 Slots</t>
+  </si>
+  <si>
+    <t>Built-in-Wifi</t>
+  </si>
+  <si>
+    <t>Max RAM Capacity</t>
+  </si>
+  <si>
+    <t>PCIe Slots</t>
+  </si>
+  <si>
+    <t>SATA Slots</t>
+  </si>
+  <si>
+    <t>ASRock</t>
+  </si>
+  <si>
+    <t>B760 PRO RS</t>
+  </si>
+  <si>
+    <t>LGA 1700</t>
+  </si>
+  <si>
+    <t>DDR5</t>
+  </si>
+  <si>
+    <t>ATX</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>256 GB</t>
+  </si>
+  <si>
+    <t>1x 5.0x16, 1x4.0x16</t>
+  </si>
+  <si>
+    <t>Asus</t>
+  </si>
+  <si>
+    <t>Prime B760-PLUS D4</t>
+  </si>
+  <si>
+    <t>DDR4</t>
+  </si>
+  <si>
+    <t>192 GB</t>
+  </si>
+  <si>
+    <t>msi</t>
+  </si>
+  <si>
+    <t>H410 Pro</t>
+  </si>
+  <si>
+    <t>LGA 1200</t>
+  </si>
+  <si>
+    <t>64 GB</t>
   </si>
   <si>
     <t xml:space="preserve">1x 3.0x16, 1x 3.0x1 </t>
   </si>
   <si>
-    <t xml:space="preserve">Medion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z370H4-EM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LGA 1151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M-ATX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32GB</t>
+    <t>Medion</t>
+  </si>
+  <si>
+    <t>Z370H4-EM</t>
+  </si>
+  <si>
+    <t>LGA 1151</t>
+  </si>
+  <si>
+    <t>M-ATX</t>
+  </si>
+  <si>
+    <t>32GB</t>
   </si>
   <si>
     <t xml:space="preserve">2x 3.0x16, 1x 3.0x1 </t>
   </si>
   <si>
-    <t xml:space="preserve">ASUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H81M-D PLUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LGA 1150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 GB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1x2.0x16, 1x2.0x1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clockspeed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boost Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i7-14700KF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4 GHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6GHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33 MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125 W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i5-12400F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5 GHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4GHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65 W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i5-10400F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9 GHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3 GHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryzen 5 5500G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6GHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2GHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i5-9400F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1 GHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i5-2500K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3 GHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7 GHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95 W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pentium G2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55 W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capacity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeamGroup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T-Create Expert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32GB x2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CL30-36-36-76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6000MT/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G.Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ripjaws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8GB x4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16-18-18-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3200MT/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corsair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vengeance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8GB x2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Micron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22-22-22-52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2800MT/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4GB x6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11-11-11-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1600MT/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VRAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VRAM Gen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clock Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCIe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gigabyte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTX 5070 OC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12GB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDDR7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2625 MHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gen 5 x16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dual 3060 Ti OC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8GB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDDR6X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1680 Mhz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gen 4 x16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix RTX 3050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDDR6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1552 MHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gen 4 x8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GTX 1660 Ti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6GB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1500 MHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gen 3 x16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GTX 1050 Ti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4GB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDDR5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1366 MHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GT 730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2GB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">902 MHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gen 2 x16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GT 710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">954 MHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gen 2 x8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zotac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GT 630</t>
-  </si>
-  <si>
-    <t xml:space="preserve">810 MHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interface</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Write Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Form factor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crucial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500GB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.2 NVMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCIe Gen 4.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,000MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,600MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSD 980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1TB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCIe Gen 3.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,000MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,500MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS50-E12-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,400MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SU650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">256GB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SATA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SATA 3.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">520MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BX500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">540MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandisk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultra G26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">515MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">545MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toschiba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160MB/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wattage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAG A850GL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">850W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80+ Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fully Modular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">corsair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CX650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">650W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80+ Bronze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non Modular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooler Master</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RS450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">550W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semi Modular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SFX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compatibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID-Cooling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FX 360 INF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">396x120x27mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AM4/5 &amp; LGA 1851 to 115X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Side Panel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fans preinstalled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MBD Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C5-White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid Tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">469x285x400mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tempered Glass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (ARGB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATX, M-ATX, ITX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fractal Design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charcoal Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447x215x469mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (Non rgb)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erazer X30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">390x190x400mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (Non rgb)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (Non rgb)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closed with small Mesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M-ATX, ITX</t>
+    <t>ASUS</t>
+  </si>
+  <si>
+    <t>H81M-D PLUS</t>
+  </si>
+  <si>
+    <t>LGA 1150</t>
+  </si>
+  <si>
+    <t>DDR3</t>
+  </si>
+  <si>
+    <t>16 GB</t>
+  </si>
+  <si>
+    <t>1x2.0x16, 1x2.0x1</t>
+  </si>
+  <si>
+    <t>Cores</t>
+  </si>
+  <si>
+    <t>Threads</t>
+  </si>
+  <si>
+    <t>Clockspeed</t>
+  </si>
+  <si>
+    <t>Boost Speed</t>
+  </si>
+  <si>
+    <t>Cache</t>
+  </si>
+  <si>
+    <t>TDP</t>
+  </si>
+  <si>
+    <t>Intel</t>
+  </si>
+  <si>
+    <t>i7-14700KF</t>
+  </si>
+  <si>
+    <t>3.4 GHz</t>
+  </si>
+  <si>
+    <t>5.6GHz</t>
+  </si>
+  <si>
+    <t>33 MB</t>
+  </si>
+  <si>
+    <t>125 W</t>
+  </si>
+  <si>
+    <t>i5-12400F</t>
+  </si>
+  <si>
+    <t>2.5 GHz</t>
+  </si>
+  <si>
+    <t>4.4GHz</t>
+  </si>
+  <si>
+    <t>18 MB</t>
+  </si>
+  <si>
+    <t>65 W</t>
+  </si>
+  <si>
+    <t>i5-10400F</t>
+  </si>
+  <si>
+    <t>2.9 GHz</t>
+  </si>
+  <si>
+    <t>4.3 GHz</t>
+  </si>
+  <si>
+    <t>12 MB</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>Ryzen 5 5500G</t>
+  </si>
+  <si>
+    <t>3.6GHz</t>
+  </si>
+  <si>
+    <t>4.2GHz</t>
+  </si>
+  <si>
+    <t>16 MB</t>
+  </si>
+  <si>
+    <t>i5-9400F</t>
+  </si>
+  <si>
+    <t>4.1 GHz</t>
+  </si>
+  <si>
+    <t>9 MB</t>
+  </si>
+  <si>
+    <t>i5-2500K</t>
+  </si>
+  <si>
+    <t>3.3 GHz</t>
+  </si>
+  <si>
+    <t>3.7 GHz</t>
+  </si>
+  <si>
+    <t>6 MB</t>
+  </si>
+  <si>
+    <t>95 W</t>
+  </si>
+  <si>
+    <t>Pentium G2020</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>3 MB</t>
+  </si>
+  <si>
+    <t>55 W</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>RGB</t>
+  </si>
+  <si>
+    <t>TeamGroup</t>
+  </si>
+  <si>
+    <t>T-Create Expert</t>
+  </si>
+  <si>
+    <t>32GB x2</t>
+  </si>
+  <si>
+    <t>CL30-36-36-76</t>
+  </si>
+  <si>
+    <t>6000MT/s</t>
+  </si>
+  <si>
+    <t>G.Skill</t>
+  </si>
+  <si>
+    <t>Ripjaws</t>
+  </si>
+  <si>
+    <t>8GB x4</t>
+  </si>
+  <si>
+    <t>16-18-18-36</t>
+  </si>
+  <si>
+    <t>3200MT/s</t>
+  </si>
+  <si>
+    <t>Corsair</t>
+  </si>
+  <si>
+    <t>Vengeance</t>
+  </si>
+  <si>
+    <t>8GB x2</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Micron</t>
+  </si>
+  <si>
+    <t>22-22-22-52</t>
+  </si>
+  <si>
+    <t>2800MT/s</t>
+  </si>
+  <si>
+    <t>4GB x6</t>
+  </si>
+  <si>
+    <t>11-11-11-28</t>
+  </si>
+  <si>
+    <t>1600MT/s</t>
+  </si>
+  <si>
+    <t>VRAM</t>
+  </si>
+  <si>
+    <t>VRAM Gen</t>
+  </si>
+  <si>
+    <t>Clock Speed</t>
+  </si>
+  <si>
+    <t>PCIe</t>
+  </si>
+  <si>
+    <t>Fans</t>
+  </si>
+  <si>
+    <t>Gigabyte</t>
+  </si>
+  <si>
+    <t>RTX 5070 OC</t>
+  </si>
+  <si>
+    <t>12GB</t>
+  </si>
+  <si>
+    <t>GDDR7</t>
+  </si>
+  <si>
+    <t>2625 MHz</t>
+  </si>
+  <si>
+    <t>Gen 5 x16</t>
+  </si>
+  <si>
+    <t>250W</t>
+  </si>
+  <si>
+    <t>Dual 3060 Ti OC</t>
+  </si>
+  <si>
+    <t>8GB</t>
+  </si>
+  <si>
+    <t>GDDR6X</t>
+  </si>
+  <si>
+    <t>1680 Mhz</t>
+  </si>
+  <si>
+    <t>Gen 4 x16</t>
+  </si>
+  <si>
+    <t>200W</t>
+  </si>
+  <si>
+    <t>Phoenix RTX 3050</t>
+  </si>
+  <si>
+    <t>GDDR6</t>
+  </si>
+  <si>
+    <t>1552 MHz</t>
+  </si>
+  <si>
+    <t>Gen 4 x8</t>
+  </si>
+  <si>
+    <t>130W</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>GTX 1660 Ti</t>
+  </si>
+  <si>
+    <t>6GB</t>
+  </si>
+  <si>
+    <t>1500 MHz</t>
+  </si>
+  <si>
+    <t>Gen 3 x16</t>
+  </si>
+  <si>
+    <t>120W</t>
+  </si>
+  <si>
+    <t>GTX 1050 Ti</t>
+  </si>
+  <si>
+    <t>4GB</t>
+  </si>
+  <si>
+    <t>GDDR5</t>
+  </si>
+  <si>
+    <t>1366 MHz</t>
+  </si>
+  <si>
+    <t>75W</t>
+  </si>
+  <si>
+    <t>GT 730</t>
+  </si>
+  <si>
+    <t>2GB</t>
+  </si>
+  <si>
+    <t>902 MHz</t>
+  </si>
+  <si>
+    <t>Gen 2 x16</t>
+  </si>
+  <si>
+    <t>23W</t>
+  </si>
+  <si>
+    <t>GT 710</t>
+  </si>
+  <si>
+    <t>954 MHz</t>
+  </si>
+  <si>
+    <t>Gen 2 x8</t>
+  </si>
+  <si>
+    <t>19W</t>
+  </si>
+  <si>
+    <t>Zotac</t>
+  </si>
+  <si>
+    <t>GT 630</t>
+  </si>
+  <si>
+    <t>810 MHz</t>
+  </si>
+  <si>
+    <t>65W</t>
+  </si>
+  <si>
+    <t>Interface</t>
+  </si>
+  <si>
+    <t>Gen</t>
+  </si>
+  <si>
+    <t>Write Speed</t>
+  </si>
+  <si>
+    <t>Read Speed</t>
+  </si>
+  <si>
+    <t>Form factor</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>RPM</t>
+  </si>
+  <si>
+    <t>crucial</t>
+  </si>
+  <si>
+    <t>P310</t>
+  </si>
+  <si>
+    <t>500GB</t>
+  </si>
+  <si>
+    <t>M.2 NVMe</t>
+  </si>
+  <si>
+    <t>PCIe Gen 4.0</t>
+  </si>
+  <si>
+    <t>5,000MB/s</t>
+  </si>
+  <si>
+    <t>6,600MB/s</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>SSD 980</t>
+  </si>
+  <si>
+    <t>1TB</t>
+  </si>
+  <si>
+    <t>PCIe Gen 3.0</t>
+  </si>
+  <si>
+    <t>3,000MB/s</t>
+  </si>
+  <si>
+    <t>3,500MB/s</t>
+  </si>
+  <si>
+    <t>Phison</t>
+  </si>
+  <si>
+    <t>PS50-E12-27</t>
+  </si>
+  <si>
+    <t>3,400MB/s</t>
+  </si>
+  <si>
+    <t>Adata</t>
+  </si>
+  <si>
+    <t>SU650</t>
+  </si>
+  <si>
+    <t>256GB</t>
+  </si>
+  <si>
+    <t>SATA</t>
+  </si>
+  <si>
+    <t>SATA 3.0</t>
+  </si>
+  <si>
+    <t>320MB/s</t>
+  </si>
+  <si>
+    <t>520MB/s</t>
+  </si>
+  <si>
+    <t>2.5”</t>
+  </si>
+  <si>
+    <t>BX500</t>
+  </si>
+  <si>
+    <t>500MB/s</t>
+  </si>
+  <si>
+    <t>540MB/s</t>
+  </si>
+  <si>
+    <t>Sandisk</t>
+  </si>
+  <si>
+    <t>Ultra G26</t>
+  </si>
+  <si>
+    <t>515MB/s</t>
+  </si>
+  <si>
+    <t>545MB/s</t>
+  </si>
+  <si>
+    <t>Toschiba</t>
+  </si>
+  <si>
+    <t>150MB/s</t>
+  </si>
+  <si>
+    <t>180MB/s</t>
+  </si>
+  <si>
+    <t>3.5”</t>
+  </si>
+  <si>
+    <t>HDD</t>
+  </si>
+  <si>
+    <t>Acer</t>
+  </si>
+  <si>
+    <t>130MB/s</t>
+  </si>
+  <si>
+    <t>160MB/s</t>
+  </si>
+  <si>
+    <t>Wattage</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Modular</t>
+  </si>
+  <si>
+    <t>MAG A850GL</t>
+  </si>
+  <si>
+    <t>850W</t>
+  </si>
+  <si>
+    <t>80+ Gold</t>
+  </si>
+  <si>
+    <t>Fully Modular</t>
+  </si>
+  <si>
+    <t>corsair</t>
+  </si>
+  <si>
+    <t>CX650</t>
+  </si>
+  <si>
+    <t>650W</t>
+  </si>
+  <si>
+    <t>80+ Bronze</t>
+  </si>
+  <si>
+    <t>Non Modular</t>
+  </si>
+  <si>
+    <t>Cooler Master</t>
+  </si>
+  <si>
+    <t>RS450</t>
+  </si>
+  <si>
+    <t>550W</t>
+  </si>
+  <si>
+    <t>Semi Modular</t>
+  </si>
+  <si>
+    <t>500W</t>
+  </si>
+  <si>
+    <t>SFX</t>
+  </si>
+  <si>
+    <t>350W</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Compatibility</t>
+  </si>
+  <si>
+    <t>ID-Cooling</t>
+  </si>
+  <si>
+    <t>FX 360 INF</t>
+  </si>
+  <si>
+    <t>AIO</t>
+  </si>
+  <si>
+    <t>396x120x27mm</t>
+  </si>
+  <si>
+    <t>AM4/5 &amp; LGA 1851 to 115X</t>
+  </si>
+  <si>
+    <t>Side Panel</t>
+  </si>
+  <si>
+    <t>Fans preinstalled</t>
+  </si>
+  <si>
+    <t>MBD Support</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Antec</t>
+  </si>
+  <si>
+    <t>C5-White</t>
+  </si>
+  <si>
+    <t>Mid Tower</t>
+  </si>
+  <si>
+    <t>469x285x400mm</t>
+  </si>
+  <si>
+    <t>Tempered Glass</t>
+  </si>
+  <si>
+    <t>7 (ARGB)</t>
+  </si>
+  <si>
+    <t>ATX, M-ATX, ITX</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Fractal Design</t>
+  </si>
+  <si>
+    <t>Charcoal Black</t>
+  </si>
+  <si>
+    <t>447x215x469mm</t>
+  </si>
+  <si>
+    <t>Mesh</t>
+  </si>
+  <si>
+    <t>5 (Non rgb)</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Erazer X30</t>
+  </si>
+  <si>
+    <t>390x190x400mm</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>3 (Non rgb)</t>
+  </si>
+  <si>
+    <t>Dell</t>
+  </si>
+  <si>
+    <t>1 (Non rgb)</t>
+  </si>
+  <si>
+    <t>ITX</t>
+  </si>
+  <si>
+    <t>Closed with small Mesh</t>
+  </si>
+  <si>
+    <t>M-ATX, ITX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -821,7 +808,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -829,119 +816,92 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -994,22 +954,21 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="1" width="11.53"/>
+    <col min="1" max="1" width="11.42578125" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1044,7 +1003,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1057,13 +1016,13 @@
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="1">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>3</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -1075,11 +1034,11 @@
       <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -1092,13 +1051,13 @@
       <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="1">
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>3</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -1110,11 +1069,11 @@
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="K3" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1127,13 +1086,13 @@
       <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="2">
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="2">
         <v>2</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -1145,11 +1104,11 @@
       <c r="J4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
@@ -1162,13 +1121,13 @@
       <c r="D5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="1">
         <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>2</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -1180,11 +1139,11 @@
       <c r="J5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="K5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -1197,13 +1156,13 @@
       <c r="D6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
@@ -1215,15 +1174,14 @@
       <c r="J6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="K6" s="1">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
@@ -1231,17 +1189,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="11.53"/>
+    <col min="1" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1267,17 +1222,17 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="1">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="1">
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -1293,17 +1248,17 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="1">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="1">
         <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -1319,17 +1274,17 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="1">
         <v>6</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="1">
         <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -1345,17 +1300,17 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="1">
         <v>6</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="1">
         <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -1371,17 +1326,17 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="1">
         <v>6</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="1">
         <v>6</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -1397,17 +1352,17 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="1">
         <v>4</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="1">
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -1423,17 +1378,17 @@
         <v>73</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="1">
         <v>2</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1449,21 +1404,20 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0"/>
-      <c r="B10" s="0"/>
-      <c r="C10" s="0"/>
-      <c r="D10" s="0"/>
-      <c r="E10" s="0"/>
-      <c r="F10" s="0"/>
-      <c r="G10" s="0"/>
-      <c r="H10" s="0"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
@@ -1471,17 +1425,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="11.53"/>
+    <col min="1" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1504,7 +1455,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>82</v>
       </c>
@@ -1527,7 +1478,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>87</v>
       </c>
@@ -1550,7 +1501,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>92</v>
       </c>
@@ -1573,7 +1524,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>96</v>
       </c>
@@ -1593,7 +1544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>96</v>
       </c>
@@ -1614,10 +1565,9 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
@@ -1625,17 +1575,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="11.53"/>
+    <col min="1" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1664,7 +1611,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>107</v>
       </c>
@@ -1683,17 +1630,17 @@
       <c r="F2" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>6144</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="I2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -1712,17 +1659,17 @@
       <c r="F3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>4864</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="I3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
@@ -1741,17 +1688,17 @@
       <c r="F4" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>2560</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="I4" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>125</v>
       </c>
@@ -1770,17 +1717,17 @@
       <c r="F5" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>1536</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="I5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -1799,17 +1746,17 @@
       <c r="F6" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>768</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="I6" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
@@ -1828,17 +1775,17 @@
       <c r="F7" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>384</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="I7" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -1857,17 +1804,17 @@
       <c r="F8" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>192</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="I8" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>145</v>
       </c>
@@ -1886,21 +1833,20 @@
       <c r="F9" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="1">
         <v>96</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="I9" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
@@ -1908,17 +1854,14 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="11.53"/>
+    <col min="1" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1950,7 +1893,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>156</v>
       </c>
@@ -1972,14 +1915,14 @@
       <c r="G2" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="1">
         <v>2230</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>164</v>
       </c>
@@ -2001,14 +1944,14 @@
       <c r="G3" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="1">
         <v>2280</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>170</v>
       </c>
@@ -2030,14 +1973,14 @@
       <c r="G4" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="1">
         <v>2280</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>173</v>
       </c>
@@ -2066,7 +2009,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>156</v>
       </c>
@@ -2095,7 +2038,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>184</v>
       </c>
@@ -2124,7 +2067,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>188</v>
       </c>
@@ -2149,11 +2092,11 @@
       <c r="I8" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="1">
         <v>7200</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>193</v>
       </c>
@@ -2178,15 +2121,14 @@
       <c r="I9" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="1">
         <v>5400</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
@@ -2194,17 +2136,14 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="11.53"/>
+    <col min="1" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2224,7 +2163,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -2244,7 +2183,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>203</v>
       </c>
@@ -2264,7 +2203,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>208</v>
       </c>
@@ -2284,7 +2223,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
@@ -2295,7 +2234,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
         <v>213</v>
       </c>
@@ -2304,10 +2243,9 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
@@ -2315,14 +2253,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2342,7 +2277,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>217</v>
       </c>
@@ -2355,7 +2290,7 @@
       <c r="D2" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2">
         <v>3</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -2364,10 +2299,9 @@
       <c r="G2" s="3"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
@@ -2375,17 +2309,14 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="11.53"/>
+    <col min="1" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2411,7 +2342,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>226</v>
       </c>
@@ -2437,7 +2368,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>234</v>
       </c>
@@ -2463,7 +2394,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -2489,7 +2420,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>244</v>
       </c>
@@ -2509,14 +2440,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
         <v>246</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -2527,10 +2458,9 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
@@ -2538,17 +2468,13 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
